--- a/outputs/1 N NO 3_ch00_measurements.xlsx
+++ b/outputs/1 N NO 3_ch00_measurements.xlsx
@@ -241,7 +241,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="23260050" cy="8020050"/>
+    <ext cx="23231475" cy="8010525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -301,7 +301,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="7143750" cy="8420100"/>
+    <ext cx="7143750" cy="8401050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1963,7 +1963,7 @@
         <v>587.1502</v>
       </c>
       <c r="D3" t="n">
-        <v>250.6931107960931</v>
+        <v>250.6931107960932</v>
       </c>
       <c r="E3" t="n">
         <v>76.637</v>
@@ -2335,7 +2335,7 @@
         <v>252.8</v>
       </c>
       <c r="D15" t="n">
-        <v>6.957010852370436</v>
+        <v>6.957010852370435</v>
       </c>
       <c r="E15" t="n">
         <v>233</v>
@@ -2428,7 +2428,7 @@
         <v>0.1753</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9441115812115525</v>
+        <v>0.9441115812115526</v>
       </c>
       <c r="E18" t="n">
         <v>-1.268</v>
